--- a/sample-data/split/Trips.xlsx
+++ b/sample-data/split/Trips.xlsx
@@ -56,13 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -496,151 +493,13 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Jaipur · Abhaneri · Ranthambore Educational Trip</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Batch 1: 12–19 December 2026 · Batch 2: 13–20 December 2026</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>A week-long educational trip for Grade 7 covering Jaipur, Abhaneri and Ranthambore, run across two batches.
-Please go through the parent and student orientation decks below before the trip. Both batches follow the same itinerary, one day apart.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Ms. Anjali Desai</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>+91 98200 11223</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>trips.grade7@example.edu</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>+91 98200 99887 (24×7 trip desk)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Grade 9</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Coorg Field Study</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>6–11 January 2027</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>A five-day field study on plantation ecology and water systems. Dates are provisional pending transport confirmation.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Mr. Vikram Nair</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>+91 98200 44556</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>trips.grade9@example.edu</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Grade 5</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Sundarbans Nature Camp</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3–6 February 2027</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>A four-day introduction to mangrove ecology, with guided boat surveys and a bird count.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ms. Fatima Sheikh</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>+91 98200 77665</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>trips.grade5@example.edu</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>+91 98200 99887 (24×7 trip desk)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
-      <formula1>"JK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
+      <formula1>"JK,SK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unrecognised status" error="Use Confirmed to show the trip as confirmed; anything else reads as &quot;coming soon&quot;." type="list">
+      <formula1>"Confirmed,Pending"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
